--- a/exports/colleges/7798_vardhman-mahavir-medical-college-vmmc-new-delhi.xlsx
+++ b/exports/colleges/7798_vardhman-mahavir-medical-college-vmmc-new-delhi.xlsx
@@ -605,7 +605,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L54"/>
+  <dimension ref="A1:L49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -617,7 +617,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="23" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
   </cols>
@@ -692,7 +692,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -702,17 +702,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>M.B.B.S.</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2.65 Lakhs</t>
+          <t>2.65 L</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5 Years 6 Months</t>
+          <t>5 years 6 months</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10+2 with 50% + NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>12 Aug - 20 Aug 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.29 Lakhs</t>
+          <t>1.29 L</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4 Years</t>
+          <t>4 years</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -784,17 +784,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>10+2 with 50% + NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Feb - 31 Mar 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -831,12 +831,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.15 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 07 Jul 2026</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Diploma in Paramedical</t>
+          <t>Diploma in Medical Lab Technician</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -888,7 +888,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Diploma in Medical Lab Technician</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10th</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Feb - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -928,7 +928,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -940,7 +940,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -950,17 +950,17 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Master of Surgery [M.S]</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.15 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -970,17 +970,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>17 Apr - 07 Jul 2026</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>PG</t>
+          <t>UG</t>
         </is>
       </c>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>MBBS</t>
+          <t>Bachelor of Science [B.Sc]</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>₹ 2.65 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>5 Years 6 Months</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>10+2 with 50% + NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Feb - 31 Mar 2026</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>B.Sc</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.}</t>
+          <t>Doctorate of Medicine [DM] (Cardiology)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>B.Sc {Hons.}</t>
+          <t>Doctorate of Medicine [DM] (Cardiology)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>₹ 1.29 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3 Years</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>10+2 with 50% + NEET</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1126,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>M.D</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>₹ 1.15 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1188,27 +1188,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>Doctorate of Medicine [DM] (Neurology)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>M.S</t>
+          <t>Doctorate of Medicine [DM] (Neurology)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>₹ 1.15 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1218,12 +1218,12 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Master of Chirurgiae [M.Ch]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>Master of Chirurgiae [M.Ch]</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>₹ 1.15 Lakhs</t>
+          <t>1.15 L</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1280,17 +1280,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>MD/DNB + NEET SS</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10 Mar - 03 Apr 2026</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -1312,27 +1312,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>DNB</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>Diplomate National Board [DNB]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>M.Ch</t>
+          <t>Diplomate National Board [DNB]</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>₹ 1.15 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1342,17 +1342,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>MS/ MD + NEET SS</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>13 May - 27 Jul 2026</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1374,27 +1374,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Diploma</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Post Graduate Diploma</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>₹ 75,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>2 years</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>1 Feb - 15 Apr 2026</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1436,27 +1436,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>BPO</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Prosthetics and Orthotics [BPO]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Bachelor of Prosthetics and Orthotics [BPO]</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>₹ 2.65 Lakhs</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 years</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1498,27 +1498,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>M.B.B.S.</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>₹ 1,000</t>
+          <t>2.65 Lakhs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years 6 Months</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1528,12 +1528,12 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% + NEET</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1560,27 +1560,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>Bachelor of Science [B.Sc] {Hons.} (Nursing)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Caution Fee</t>
+          <t>Bachelor of Science [B.Sc] {Hons.} (Nursing)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>₹ 10,000</t>
+          <t>1.29 Lakhs</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>4 Years</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1590,12 +1590,12 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% + NEET</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1622,27 +1622,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>University Fee</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>University Fee</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>University Fee</t>
+          <t>Doctor of Medicine [MD]</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>₹ 94,000</t>
+          <t>1.15 Lakhs</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1672,7 +1672,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1684,27 +1684,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alumni Fee</t>
+          <t>Diploma in Paramedical</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alumni Fee</t>
+          <t>Diploma in Medical Lab Technician</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Alumni Fee</t>
+          <t>Diploma in Medical Lab Technician</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>₹ 2,000</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10th</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1746,27 +1746,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Miscellaneous Fee</t>
+          <t>Master of Surgery [M.S]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>₹ 21,500</t>
+          <t>1.15 Lakhs</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET PG</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>PG</t>
         </is>
       </c>
     </row>
@@ -1808,27 +1808,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>MBBS</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>₹ 1.29 Lakhs</t>
+          <t>₹ 2.65 Lakhs</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>5 Years 6 Months</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% + NEET</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>B.Sc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>B.Sc {Hons.}</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>B.Sc {Hons.}</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>₹250</t>
+          <t>₹ 1.29 Lakhs</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>10+2 with 50% + NEET</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1932,22 +1932,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Caution Fee *</t>
+          <t>M.D</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>₹10000</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1994,22 +1994,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>University Fees</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>University Fees</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>University Fees</t>
+          <t>M.S</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>₹23500</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Alumni Fees</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Alumni Fees</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Alumni Fees</t>
+          <t>DM</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>₹2000</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -2086,12 +2086,12 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>MD/DNB + NEET SS</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2118,27 +2118,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Miscellaneous Fees</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>₹5375</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>3 Years</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>MS/ MD + NEET SS</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>NEET SS</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>UG</t>
+          <t>Doctorate</t>
         </is>
       </c>
     </row>
@@ -2180,22 +2180,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesiology</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesiology</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Anaesthesiology</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>₹41125</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2210,7 +2210,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2242,17 +2242,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprology</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprology</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tuition Fee</t>
+          <t>Dermatology, Venereology &amp; Leprology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2304,17 +2304,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Total Fee</t>
+          <t>Paediatrics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tuition Fees</t>
+          <t>Radiotherapy</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>₹54500</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2428,22 +2428,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Yearly Fees</t>
+          <t>Pathology</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>₹54500</t>
+          <t>₹ 1.15 Lakhs</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2458,7 +2458,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Graduation + NEET PG</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Anaesthesiology</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Anaesthesiology</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Anaesthesiology</t>
+          <t>Biochemistry</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2552,17 +2552,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Dermatology, Venereology &amp; Leprology</t>
+          <t>Anatomy</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dermatology, Venereology &amp; Leprology</t>
+          <t>Anatomy</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Dermatology, Venereology &amp; Leprology</t>
+          <t>Anatomy</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2614,17 +2614,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Paediatrics</t>
+          <t>Community Medicine</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Paediatrics</t>
+          <t>Community Medicine</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paediatrics</t>
+          <t>Community Medicine</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2676,17 +2676,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Radiotherapy</t>
+          <t>Forensic Medicine</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2738,17 +2738,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Pathology</t>
+          <t>Microbiology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2800,17 +2800,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Biochemistry</t>
+          <t>Pharmacology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2862,17 +2862,17 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Anatomy</t>
+          <t>Physical Medicine And Rehabilitation</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Anatomy</t>
+          <t>Physical Medicine And Rehabilitation</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Anatomy</t>
+          <t>Physical Medicine And Rehabilitation</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -2924,17 +2924,17 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Community Medicine</t>
+          <t>Physiology</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Community Medicine</t>
+          <t>Physiology</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Community Medicine</t>
+          <t>Physiology</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Forensic Medicine</t>
+          <t>Psychiatry</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -3048,17 +3048,17 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Radiodiagnosis</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Radiodiagnosis</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Microbiology</t>
+          <t>Radiodiagnosis</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -3110,17 +3110,17 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Pharmacology</t>
+          <t>Sports Medicine</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -3172,17 +3172,17 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Physical Medicine And Rehabilitation</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Physical Medicine And Rehabilitation</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Physical Medicine And Rehabilitation</t>
+          <t>Obstetrics &amp; Gynaecology</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3234,17 +3234,17 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Physiology</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Physiology</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Physiology</t>
+          <t>E.N.T.</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Psychiatry</t>
+          <t>Ophthalmology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -3358,17 +3358,17 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Radiodiagnosis</t>
+          <t>Orthopaedics</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Radiodiagnosis</t>
+          <t>Orthopaedics</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Radiodiagnosis</t>
+          <t>Orthopaedics</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -3420,17 +3420,17 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Sports Medicine</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Sports Medicine</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Sports Medicine</t>
+          <t>Nephrology</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>MD/DNB + NEET SS</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3482,17 +3482,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Obstetrics &amp; Gynaecology</t>
+          <t>Neurology</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>MD/DNB + NEET SS</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>E.N.T.</t>
+          <t>Pulmonary Medicine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>E.N.T.</t>
+          <t>Pulmonary Medicine</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>E.N.T.</t>
+          <t>Pulmonary Medicine</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3574,7 +3574,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>MD/DNB + NEET SS</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3606,29 +3606,25 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>M.Ch</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>M.Ch (General)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Ophthalmology</t>
+          <t>General</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>₹ 1.15 Lakhs</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
+          <t>MS/ MD + NEET SS</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr">
         <is>
           <t>Full Time</t>
@@ -3636,7 +3632,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Graduation + NEET PG</t>
+          <t>Not Specified</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3655,312 +3651,6 @@
         </is>
       </c>
       <c r="L49" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Orthopaedics</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Orthopaedics</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Orthopaedics</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>₹ 1.15 Lakhs</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Graduation + NEET PG</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Nephrology</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nephrology</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nephrology</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>₹ 1.15 Lakhs</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>MD/DNB + NEET SS</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Neurology</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Neurology</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Neurology</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>₹ 1.15 Lakhs</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>MD/DNB + NEET SS</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Pulmonary Medicine</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pulmonary Medicine</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Pulmonary Medicine</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>₹ 1.15 Lakhs</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>MD/DNB + NEET SS</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>UG</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>7798</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>M.Ch</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>M.Ch (General)</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>General</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>MS/ MD + NEET SS</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Full Time</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Not Specified</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
         <is>
           <t>UG</t>
         </is>
